--- a/data/belgeler/2023 tatil ve aylık saatler.xlsx
+++ b/data/belgeler/2023 tatil ve aylık saatler.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Python Program\REPYS-main\RADPYS\data\belgeler\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Yeni klasör\REPYS\RADPYS-1\data\belgeler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF887E3-E4FD-41C4-ACCF-FF29AB006F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB98B0A9-A254-48B3-8C17-4762E23A2937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2022" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="42">
   <si>
     <t>Yılbaşı</t>
   </si>
@@ -97,15 +97,6 @@
     <t>12 SAAT MESAİ ÇALIŞMA SAATİ</t>
   </si>
   <si>
-    <t>Cuma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuma </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Çarşamba </t>
-  </si>
-  <si>
     <t>Toplam</t>
   </si>
   <si>
@@ -115,12 +106,6 @@
     <t>24 SAAT NÖBET SAYISI</t>
   </si>
   <si>
-    <t>Kurban Bayramı Arefe</t>
-  </si>
-  <si>
-    <t>İdari İzin</t>
-  </si>
-  <si>
     <t>Yıllık İzin (1 gün)</t>
   </si>
   <si>
@@ -137,6 +122,48 @@
   </si>
   <si>
     <t>Yıllık İzin (2 gün)</t>
+  </si>
+  <si>
+    <t>Ramazan Bayramı Arifesi</t>
+  </si>
+  <si>
+    <t>Ramazan Bayramı 1.gün</t>
+  </si>
+  <si>
+    <t>Ramazan Bayramı 2.gün</t>
+  </si>
+  <si>
+    <t>Ramazan Bayramı 3.gün</t>
+  </si>
+  <si>
+    <t>Atatürk’ü Anma Gençlik ve Spor Bayramı</t>
+  </si>
+  <si>
+    <t>Kurban Bayramı Arifesi</t>
+  </si>
+  <si>
+    <t>Kurban Bayramı 1.gün</t>
+  </si>
+  <si>
+    <t>Kurban Bayramı 2.gün</t>
+  </si>
+  <si>
+    <t>Kurban Bayramı 3.gün</t>
+  </si>
+  <si>
+    <t>Kurban Bayramı 4.gün</t>
+  </si>
+  <si>
+    <t>Demokrasi ve Millî Birlik Günü</t>
+  </si>
+  <si>
+    <t>Cumhuriyet Bayramı Arifesi</t>
+  </si>
+  <si>
+    <t>Yılbaşı gecesi</t>
+  </si>
+  <si>
+    <t>24 SAAT MESAİ ÇALIŞMA SAATİ</t>
   </si>
 </sst>
 </file>
@@ -146,7 +173,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="hh:mm;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,22 +206,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF212529"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -202,21 +213,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="18">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -356,45 +361,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -463,7 +429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -474,33 +440,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -520,13 +463,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -535,9 +478,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -833,17 +785,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E1" s="10"/>
-      <c r="F1" s="11" t="s">
+      <c r="E1" s="9"/>
+      <c r="F1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -857,22 +809,22 @@
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="8">
         <v>44576</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="17">
         <f>NETWORKDAYS(E2,E3,A2:A84)</f>
         <v>21</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="19">
         <f>F2*7</f>
         <v>147</v>
       </c>
-      <c r="H2" s="29">
+      <c r="H2" s="17">
         <f>NETWORKDAYS(E2,E3,A2:A17)</f>
         <v>21</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="18">
         <f t="shared" ref="I2" si="0">H2*12</f>
         <v>252</v>
       </c>
@@ -890,10 +842,10 @@
       <c r="E3" s="6">
         <v>44606</v>
       </c>
-      <c r="F3" s="23"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="27"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -908,19 +860,19 @@
       <c r="E4" s="5">
         <v>44607</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="17">
         <f>NETWORKDAYS(E4,E5,A2:A86)</f>
         <v>20</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="13">
         <f t="shared" ref="G4" si="1">F4*7</f>
         <v>140</v>
       </c>
-      <c r="H4" s="29">
+      <c r="H4" s="17">
         <f>NETWORKDAYS(E4,E5,A2:A17)</f>
         <v>20</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="15">
         <f t="shared" ref="I4" si="2">H4*12</f>
         <v>240</v>
       </c>
@@ -938,10 +890,10 @@
       <c r="E5" s="6">
         <v>44634</v>
       </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="27"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -956,19 +908,19 @@
       <c r="E6" s="5">
         <v>44635</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="17">
         <f>NETWORKDAYS(E6,E7,A2:A88)</f>
         <v>23</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="13">
         <f t="shared" ref="G6" si="3">F6*7</f>
         <v>161</v>
       </c>
-      <c r="H6" s="29">
+      <c r="H6" s="17">
         <f>NETWORKDAYS(E6,E7,A2:A17)</f>
         <v>23</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="15">
         <f t="shared" ref="I6" si="4">H6*12</f>
         <v>276</v>
       </c>
@@ -986,10 +938,10 @@
       <c r="E7" s="6">
         <v>44665</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="27"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1004,19 +956,19 @@
       <c r="E8" s="5">
         <v>44677</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="17">
         <f>NETWORKDAYS(E8,E9,A2:A90)</f>
         <v>11</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="13">
         <f t="shared" ref="G8" si="5">F8*7</f>
         <v>77</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="17">
         <f>NETWORKDAYS(E8,E9,A2:A17)</f>
         <v>11</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="15">
         <f t="shared" ref="I8" si="6">H8*12</f>
         <v>132</v>
       </c>
@@ -1034,10 +986,10 @@
       <c r="E9" s="6">
         <v>44695</v>
       </c>
-      <c r="F9" s="23"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="27"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1052,19 +1004,19 @@
       <c r="E10" s="5">
         <v>44696</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="17">
         <f>NETWORKDAYS(E10,E11,A2:A92)</f>
         <v>21</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="13">
         <f t="shared" ref="G10" si="7">F10*7</f>
         <v>147</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="17">
         <f>NETWORKDAYS(E10,E11,A2:A17)</f>
         <v>21</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="15">
         <f t="shared" ref="I10" si="8">H10*12</f>
         <v>252</v>
       </c>
@@ -1082,10 +1034,10 @@
       <c r="E11" s="6">
         <v>44726</v>
       </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="27"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="16"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1100,19 +1052,19 @@
       <c r="E12" s="5">
         <v>44727</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="17">
         <f>NETWORKDAYS(E12,E13,A2:A94)</f>
         <v>18</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="13">
         <f t="shared" ref="G12" si="9">F12*7</f>
         <v>126</v>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="17">
         <f>NETWORKDAYS(E12,E13,A2:A17)</f>
         <v>18</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="15">
         <f t="shared" ref="I12" si="10">H12*12</f>
         <v>216</v>
       </c>
@@ -1131,10 +1083,10 @@
       <c r="E13" s="6">
         <v>44756</v>
       </c>
-      <c r="F13" s="23"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="27"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="16"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1149,19 +1101,19 @@
       <c r="E14" s="5">
         <v>44757</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="17">
         <f>NETWORKDAYS(E14,E15,A2:A96)</f>
         <v>20</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="13">
         <f t="shared" ref="G14" si="11">F14*7</f>
         <v>140</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="17">
         <f>NETWORKDAYS(E14,E15,A2:A17)</f>
         <v>20</v>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="15">
         <f>H14*12</f>
         <v>240</v>
       </c>
@@ -1179,17 +1131,17 @@
       <c r="E15" s="6">
         <v>44787</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="27"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="16"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>44755</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>13</v>
@@ -1197,19 +1149,19 @@
       <c r="E16" s="5">
         <v>44788</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="17">
         <f>NETWORKDAYS(E16,E17,A2:A98)</f>
         <v>22</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="13">
         <f t="shared" ref="G16" si="12">F16*7</f>
         <v>154</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="17">
         <f>NETWORKDAYS(E16,E17,A2:A17)</f>
         <v>22</v>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="15">
         <f t="shared" ref="I16" si="13">H16*12</f>
         <v>264</v>
       </c>
@@ -1219,7 +1171,7 @@
         <v>44756</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>14</v>
@@ -1227,29 +1179,29 @@
       <c r="E17" s="6">
         <v>44818</v>
       </c>
-      <c r="F17" s="23"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="27"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="16"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="E18" s="5">
         <v>44819</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="17">
         <f>NETWORKDAYS(E18,E19,A2:A100)</f>
         <v>22</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="13">
         <f t="shared" ref="G18" si="14">F18*7</f>
         <v>154</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="17">
         <f>NETWORKDAYS(E18,E19,A2:A17)</f>
         <v>22</v>
       </c>
-      <c r="I18" s="26">
+      <c r="I18" s="15">
         <f t="shared" ref="I18" si="15">H18*12</f>
         <v>264</v>
       </c>
@@ -1259,29 +1211,29 @@
       <c r="E19" s="6">
         <v>44848</v>
       </c>
-      <c r="F19" s="23"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="27"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="16"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="E20" s="5">
         <v>44849</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="17">
         <f>NETWORKDAYS(E20,E21,A2:A102)</f>
         <v>21</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="13">
         <f t="shared" ref="G20" si="16">F20*7</f>
         <v>147</v>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="17">
         <f>NETWORKDAYS(E20,E21,A2:A17)</f>
         <v>21</v>
       </c>
-      <c r="I20" s="26">
+      <c r="I20" s="15">
         <f t="shared" ref="I20" si="17">H20*12</f>
         <v>252</v>
       </c>
@@ -1291,29 +1243,29 @@
       <c r="E21" s="6">
         <v>44879</v>
       </c>
-      <c r="F21" s="23"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="27"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="16"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="E22" s="5">
         <v>44880</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="17">
         <f>NETWORKDAYS(E22,E23,A2:A104)</f>
         <v>22</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="13">
         <f t="shared" ref="G22" si="18">F22*7</f>
         <v>154</v>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="17">
         <f>NETWORKDAYS(E22,E23,A2:A17)</f>
         <v>22</v>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="15">
         <f t="shared" ref="I22" si="19">H22*12</f>
         <v>264</v>
       </c>
@@ -1323,29 +1275,29 @@
       <c r="E23" s="6">
         <v>44909</v>
       </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="27"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="16"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="E24" s="5">
         <v>44910</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="17">
         <f>NETWORKDAYS(E24,E25,A2:A106)</f>
         <v>22</v>
       </c>
-      <c r="G24" s="24">
+      <c r="G24" s="13">
         <f t="shared" ref="G24" si="20">F24*7</f>
         <v>154</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="17">
         <f>NETWORKDAYS(E24,E25,A2:A17)</f>
         <v>22</v>
       </c>
-      <c r="I24" s="26">
+      <c r="I24" s="15">
         <f t="shared" ref="I24" si="21">H24*12</f>
         <v>264</v>
       </c>
@@ -1355,27 +1307,27 @@
       <c r="E25" s="6">
         <v>44940</v>
       </c>
-      <c r="F25" s="23"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="27"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="16"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="E26" s="5"/>
-      <c r="F26" s="22">
+      <c r="F26" s="11">
         <f>SUM(F2:F25)</f>
         <v>243</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="11">
         <f>SUM(G2:G25)</f>
         <v>1701</v>
       </c>
-      <c r="H26" s="24">
+      <c r="H26" s="13">
         <f>SUM(H2:H25)</f>
         <v>243</v>
       </c>
-      <c r="I26" s="26">
+      <c r="I26" s="15">
         <f>H26*12</f>
         <v>2916</v>
       </c>
@@ -1383,10 +1335,10 @@
     <row r="27" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="27"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="16"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
@@ -1475,19 +1427,36 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="I24:I25"/>
     <mergeCell ref="G26:G27"/>
@@ -1497,36 +1466,19 @@
     <mergeCell ref="H24:H25"/>
     <mergeCell ref="G22:G23"/>
     <mergeCell ref="G24:G25"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="F20:F21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1549,17 +1501,17 @@
     <row r="1" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="11" t="s">
+      <c r="E1" s="9"/>
+      <c r="F1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1573,21 +1525,21 @@
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="8">
         <v>44562</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="17">
         <f>NETWORKDAYS(E2,E3,A2:A200)</f>
         <v>219</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="19">
         <f>F2*7</f>
         <v>1533</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="19">
         <v>12</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="18">
         <f t="shared" ref="I2" si="0">H2*12</f>
         <v>144</v>
       </c>
@@ -1605,10 +1557,10 @@
       <c r="E3" s="6">
         <v>44926</v>
       </c>
-      <c r="F3" s="23"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="27"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1621,10 +1573,10 @@
         <v>10</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="26"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="15"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
@@ -1637,10 +1589,10 @@
         <v>11</v>
       </c>
       <c r="E5" s="6"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="27"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1653,10 +1605,10 @@
         <v>12</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="26"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="15"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
@@ -1669,10 +1621,10 @@
         <v>13</v>
       </c>
       <c r="E7" s="6"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="27"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1685,10 +1637,10 @@
         <v>14</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="26"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="15"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
@@ -1701,10 +1653,10 @@
         <v>9</v>
       </c>
       <c r="E9" s="6"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="27"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1717,10 +1669,10 @@
         <v>10</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="26"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="15"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
@@ -1733,10 +1685,10 @@
         <v>11</v>
       </c>
       <c r="E11" s="6"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="27"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="16"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1749,10 +1701,10 @@
         <v>12</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="26"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="15"/>
     </row>
     <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
@@ -1766,10 +1718,10 @@
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="27"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="16"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1782,10 +1734,10 @@
         <v>12</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="26"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="15"/>
     </row>
     <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
@@ -1798,375 +1750,344 @@
         <v>9</v>
       </c>
       <c r="E15" s="6"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="27"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="16"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>44755</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="5"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="26"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="15"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>44756</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E17" s="6"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="27"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="16"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>44827</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C18" s="2"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="26"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="15"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>44881</v>
       </c>
-      <c r="B19" s="31" t="s">
-        <v>28</v>
+      <c r="B19" s="20" t="s">
+        <v>23</v>
       </c>
       <c r="C19" s="2"/>
       <c r="E19" s="6"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="27"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="16"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>44882</v>
       </c>
-      <c r="B20" s="31"/>
+      <c r="B20" s="20"/>
       <c r="C20" s="2"/>
       <c r="E20" s="5"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="26"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="15"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>44883</v>
       </c>
-      <c r="B21" s="31"/>
+      <c r="B21" s="20"/>
       <c r="C21" s="2"/>
       <c r="E21" s="6"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="27"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="16"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>44884</v>
       </c>
-      <c r="B22" s="31"/>
+      <c r="B22" s="20"/>
       <c r="C22" s="2"/>
       <c r="E22" s="5"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="26"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="15"/>
     </row>
     <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>44885</v>
       </c>
-      <c r="B23" s="31"/>
+      <c r="B23" s="20"/>
       <c r="C23" s="2"/>
       <c r="E23" s="6"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="27"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="16"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>44886</v>
       </c>
-      <c r="B24" s="31"/>
+      <c r="B24" s="20"/>
       <c r="C24" s="2"/>
       <c r="E24" s="5"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="26"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="15"/>
     </row>
     <row r="25" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>44887</v>
       </c>
-      <c r="B25" s="31"/>
+      <c r="B25" s="20"/>
       <c r="C25" s="2"/>
       <c r="E25" s="6"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="27"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="16"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>44888</v>
       </c>
-      <c r="B26" s="31"/>
+      <c r="B26" s="20"/>
       <c r="C26" s="2"/>
       <c r="E26" s="5"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="26"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="15"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>44889</v>
       </c>
-      <c r="B27" s="31"/>
+      <c r="B27" s="20"/>
       <c r="C27" s="2"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="27"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="16"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>44890</v>
       </c>
-      <c r="B28" s="31"/>
+      <c r="B28" s="20"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>44760</v>
       </c>
-      <c r="B29" s="32" t="s">
-        <v>29</v>
+      <c r="B29" s="21" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>44761</v>
       </c>
-      <c r="B30" s="32"/>
+      <c r="B30" s="21"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>44762</v>
       </c>
-      <c r="B31" s="32"/>
+      <c r="B31" s="21"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>44763</v>
       </c>
-      <c r="B32" s="32"/>
+      <c r="B32" s="21"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>44764</v>
       </c>
-      <c r="B33" s="32"/>
+      <c r="B33" s="21"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>44765</v>
       </c>
-      <c r="B34" s="32"/>
+      <c r="B34" s="21"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>44766</v>
       </c>
-      <c r="B35" s="32"/>
+      <c r="B35" s="21"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>44767</v>
       </c>
-      <c r="B36" s="32"/>
+      <c r="B36" s="21"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>44768</v>
       </c>
-      <c r="B37" s="32"/>
+      <c r="B37" s="21"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>44769</v>
       </c>
-      <c r="B38" s="32"/>
+      <c r="B38" s="21"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>44770</v>
       </c>
-      <c r="B39" s="32"/>
+      <c r="B39" s="21"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>44771</v>
       </c>
-      <c r="B40" s="32"/>
+      <c r="B40" s="21"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>44592</v>
       </c>
-      <c r="B41" s="31" t="s">
-        <v>30</v>
+      <c r="B41" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>44593</v>
       </c>
-      <c r="B42" s="31"/>
+      <c r="B42" s="20"/>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>44594</v>
       </c>
-      <c r="B43" s="31"/>
+      <c r="B43" s="20"/>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>44595</v>
       </c>
-      <c r="B44" s="31"/>
+      <c r="B44" s="20"/>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44596</v>
       </c>
-      <c r="B45" s="31"/>
+      <c r="B45" s="20"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44788</v>
       </c>
-      <c r="B46" s="32" t="s">
-        <v>31</v>
+      <c r="B46" s="21" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>44789</v>
       </c>
-      <c r="B47" s="32"/>
+      <c r="B47" s="21"/>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>44790</v>
       </c>
-      <c r="B48" s="32"/>
+      <c r="B48" s="21"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>44791</v>
       </c>
-      <c r="B49" s="32"/>
+      <c r="B49" s="21"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>44792</v>
       </c>
-      <c r="B50" s="32"/>
+      <c r="B50" s="21"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>44793</v>
       </c>
-      <c r="B51" s="32"/>
+      <c r="B51" s="21"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>44794</v>
       </c>
-      <c r="B52" s="32"/>
+      <c r="B52" s="21"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>44686</v>
       </c>
-      <c r="B53" s="32" t="s">
-        <v>32</v>
+      <c r="B53" s="21" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>44687</v>
       </c>
-      <c r="B54" s="32"/>
+      <c r="B54" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="B41:B45"/>
+    <mergeCell ref="B46:B52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G26:G27"/>
     <mergeCell ref="H26:H27"/>
     <mergeCell ref="I26:I27"/>
     <mergeCell ref="B19:B28"/>
@@ -2183,11 +2104,42 @@
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="H18:H19"/>
     <mergeCell ref="I18:I19"/>
-    <mergeCell ref="B41:B45"/>
-    <mergeCell ref="B46:B52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2195,669 +2147,662 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="3" width="39.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
     <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" customWidth="1"/>
     <col min="8" max="8" width="11.85546875" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="33" t="s">
+      <c r="C1" s="27"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="33" t="s">
+      <c r="I1" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="23" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="13">
-        <v>44927</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="12" t="s">
+      <c r="K1" s="23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="16">
-        <v>44927</v>
-      </c>
-      <c r="F2" s="22">
+      <c r="E2" s="24">
+        <v>46023</v>
+      </c>
+      <c r="F2" s="25">
         <f>NETWORKDAYS(E2,E3,A2:A31)</f>
-        <v>22</v>
-      </c>
-      <c r="G2" s="24">
+        <v>21</v>
+      </c>
+      <c r="G2" s="25">
         <f>F2*7</f>
-        <v>154</v>
-      </c>
-      <c r="H2" s="24">
-        <v>13</v>
-      </c>
-      <c r="I2" s="22">
-        <v>6.5</v>
-      </c>
-      <c r="J2" s="26">
+        <v>147</v>
+      </c>
+      <c r="H2" s="25">
+        <v>12</v>
+      </c>
+      <c r="I2" s="25">
+        <v>6</v>
+      </c>
+      <c r="J2" s="25">
         <f t="shared" ref="J2" si="0">H2*12</f>
-        <v>156</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14">
-        <v>45037</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="17">
-        <v>44957</v>
-      </c>
-      <c r="F3" s="23"/>
+        <v>144</v>
+      </c>
+      <c r="K2" s="25">
+        <f>I2*24</f>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="24">
+        <v>46053</v>
+      </c>
+      <c r="F3" s="25"/>
       <c r="G3" s="25"/>
       <c r="H3" s="25"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="27"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
-        <v>45038</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="16">
-        <v>44958</v>
-      </c>
-      <c r="F4" s="22">
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="24">
+        <v>46054</v>
+      </c>
+      <c r="F4" s="25">
         <f>NETWORKDAYS(E4,E5,A2:A31)</f>
         <v>20</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="25">
         <f t="shared" ref="G4" si="1">F4*7</f>
         <v>140</v>
       </c>
-      <c r="H4" s="24">
+      <c r="H4" s="25">
         <v>12</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="25">
         <v>6</v>
       </c>
-      <c r="J4" s="26">
+      <c r="J4" s="25">
         <f t="shared" ref="J4" si="2">H4*12</f>
         <v>144</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13">
-        <v>45039</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="17">
-        <v>44985</v>
-      </c>
-      <c r="F5" s="23"/>
+      <c r="K4" s="25">
+        <f t="shared" ref="K4:K25" si="3">I4*24</f>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>46102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="24">
+        <v>46081</v>
+      </c>
+      <c r="F5" s="25"/>
       <c r="G5" s="25"/>
       <c r="H5" s="25"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="27"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="13">
-        <v>45039</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="12" t="s">
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>46103</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="24">
+        <v>46082</v>
+      </c>
+      <c r="F6" s="25">
+        <f>NETWORKDAYS(E6,E7,A2:A31)</f>
+        <v>20</v>
+      </c>
+      <c r="G6" s="25">
+        <f t="shared" ref="G6" si="4">F6*7</f>
+        <v>140</v>
+      </c>
+      <c r="H6" s="25">
+        <v>12</v>
+      </c>
+      <c r="I6" s="25">
+        <v>6</v>
+      </c>
+      <c r="J6" s="25">
+        <f t="shared" ref="J6" si="5">H6*12</f>
+        <v>144</v>
+      </c>
+      <c r="K6" s="25">
+        <f t="shared" ref="K6:K25" si="6">I6*24</f>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B7" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="16">
-        <v>44986</v>
-      </c>
-      <c r="F6" s="22">
-        <f>NETWORKDAYS(E6,E7,A2:A31)</f>
-        <v>23</v>
-      </c>
-      <c r="G6" s="24">
-        <f t="shared" ref="G6" si="3">F6*7</f>
-        <v>161</v>
-      </c>
-      <c r="H6" s="24">
-        <v>13</v>
-      </c>
-      <c r="I6" s="22">
-        <v>6.5</v>
-      </c>
-      <c r="J6" s="26">
-        <f t="shared" ref="J6" si="4">H6*12</f>
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
-        <v>45047</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="17">
-        <v>45016</v>
-      </c>
-      <c r="F7" s="23"/>
+      <c r="E7" s="24">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="25"/>
       <c r="G7" s="25"/>
       <c r="H7" s="25"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="27"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
-        <v>45065</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="16">
-        <v>45017</v>
-      </c>
-      <c r="F8" s="22">
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="24">
+        <v>46113</v>
+      </c>
+      <c r="F8" s="25">
         <f>NETWORKDAYS(E8,E9,A2:A31)</f>
-        <v>19</v>
-      </c>
-      <c r="G8" s="24">
-        <f t="shared" ref="G8" si="5">F8*7</f>
-        <v>133</v>
-      </c>
-      <c r="H8" s="24">
-        <v>11</v>
-      </c>
-      <c r="I8" s="22">
-        <v>5.5</v>
-      </c>
-      <c r="J8" s="26">
-        <f t="shared" ref="J8" si="6">H8*12</f>
-        <v>132</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
-        <v>45105</v>
-      </c>
-      <c r="B9" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="17">
-        <v>45046</v>
-      </c>
-      <c r="F9" s="23"/>
+      <c r="G8" s="25">
+        <f t="shared" ref="G8" si="7">F8*7</f>
+        <v>147</v>
+      </c>
+      <c r="H8" s="25">
+        <v>12</v>
+      </c>
+      <c r="I8" s="25">
+        <v>6</v>
+      </c>
+      <c r="J8" s="25">
+        <f t="shared" ref="J8" si="8">H8*12</f>
+        <v>144</v>
+      </c>
+      <c r="K8" s="25">
+        <f t="shared" ref="K8:K25" si="9">I8*24</f>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="24">
+        <v>46142</v>
+      </c>
+      <c r="F9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="27"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
-        <v>45106</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="16">
-        <v>45047</v>
-      </c>
-      <c r="F10" s="22">
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="24">
+        <v>46143</v>
+      </c>
+      <c r="F10" s="25">
         <f>NETWORKDAYS(E10,E11,A2:A31)</f>
-        <v>21</v>
-      </c>
-      <c r="G10" s="24">
-        <f t="shared" ref="G10" si="7">F10*7</f>
-        <v>147</v>
-      </c>
-      <c r="H10" s="24">
-        <v>12</v>
-      </c>
-      <c r="I10" s="22">
-        <v>6</v>
-      </c>
-      <c r="J10" s="26">
-        <f t="shared" ref="J10" si="8">H10*12</f>
-        <v>144</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14">
-        <v>45107</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="17">
-        <v>45077</v>
-      </c>
-      <c r="F11" s="23"/>
+        <v>15</v>
+      </c>
+      <c r="G10" s="25">
+        <f t="shared" ref="G10" si="10">F10*7</f>
+        <v>105</v>
+      </c>
+      <c r="H10" s="25">
+        <v>9</v>
+      </c>
+      <c r="I10" s="25">
+        <v>4.5</v>
+      </c>
+      <c r="J10" s="25">
+        <f t="shared" ref="J10" si="11">H10*12</f>
+        <v>108</v>
+      </c>
+      <c r="K10" s="25">
+        <f t="shared" ref="K10:K25" si="12">I10*24</f>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="24">
+        <v>46173</v>
+      </c>
+      <c r="F11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="27"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="13">
-        <v>45108</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="16">
-        <v>45078</v>
-      </c>
-      <c r="F12" s="22">
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="24">
+        <v>46174</v>
+      </c>
+      <c r="F12" s="25">
         <f>NETWORKDAYS(E12,E13,A2:A31)</f>
-        <v>17</v>
-      </c>
-      <c r="G12" s="24">
-        <f t="shared" ref="G12" si="9">F12*7</f>
-        <v>119</v>
-      </c>
-      <c r="H12" s="24">
-        <v>10</v>
-      </c>
-      <c r="I12" s="22">
-        <v>5</v>
-      </c>
-      <c r="J12" s="26">
-        <f t="shared" ref="J12" si="10">H12*12</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="13">
-        <v>45122</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="17">
-        <v>45107</v>
-      </c>
-      <c r="F13" s="23"/>
+        <v>22</v>
+      </c>
+      <c r="G12" s="25">
+        <f t="shared" ref="G12" si="13">F12*7</f>
+        <v>154</v>
+      </c>
+      <c r="H12" s="25">
+        <v>13</v>
+      </c>
+      <c r="I12" s="25">
+        <v>6.5</v>
+      </c>
+      <c r="J12" s="25">
+        <f t="shared" ref="J12" si="14">H12*12</f>
+        <v>156</v>
+      </c>
+      <c r="K12" s="25">
+        <f t="shared" ref="K12:K25" si="15">I12*24</f>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="24">
+        <v>46203</v>
+      </c>
+      <c r="F13" s="25"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="27"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="14">
-        <v>45168</v>
-      </c>
-      <c r="B14" s="15" t="s">
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="24">
+        <v>46204</v>
+      </c>
+      <c r="F14" s="25">
+        <f>NETWORKDAYS(E14,E15,A2:A31)</f>
+        <v>22</v>
+      </c>
+      <c r="G14" s="25">
+        <f t="shared" ref="G14" si="16">F14*7</f>
+        <v>154</v>
+      </c>
+      <c r="H14" s="25">
         <v>13</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="16">
-        <v>45108</v>
-      </c>
-      <c r="F14" s="22">
-        <f>NETWORKDAYS(E14,E15,A2:A31)</f>
-        <v>21</v>
-      </c>
-      <c r="G14" s="24">
-        <f t="shared" ref="G14" si="11">F14*7</f>
-        <v>147</v>
-      </c>
-      <c r="H14" s="24">
-        <v>12</v>
-      </c>
-      <c r="I14" s="22">
-        <v>6</v>
-      </c>
-      <c r="J14" s="26">
+      <c r="I14" s="25">
+        <v>6.5</v>
+      </c>
+      <c r="J14" s="25">
         <f>H14*12</f>
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="13">
-        <v>45228</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="17">
-        <v>45138</v>
-      </c>
-      <c r="F15" s="23"/>
+        <v>156</v>
+      </c>
+      <c r="K14" s="25">
+        <f t="shared" ref="K14:K25" si="17">I14*24</f>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="24">
+        <v>46234</v>
+      </c>
+      <c r="F15" s="25"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="27"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="18">
-        <v>45103</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="16">
-        <v>45139</v>
-      </c>
-      <c r="F16" s="22">
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46264</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="24">
+        <v>46235</v>
+      </c>
+      <c r="F16" s="25">
         <f>NETWORKDAYS(E16,E17,A2:A31)</f>
-        <v>22</v>
-      </c>
-      <c r="G16" s="24">
-        <f t="shared" ref="G16" si="12">F16*7</f>
-        <v>154</v>
-      </c>
-      <c r="H16" s="24">
-        <v>13</v>
-      </c>
-      <c r="I16" s="22">
-        <v>6.5</v>
-      </c>
-      <c r="J16" s="26">
-        <f t="shared" ref="J16" si="13">H16*12</f>
-        <v>156</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="18">
-        <v>45104</v>
-      </c>
-      <c r="B17" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="25">
+        <f t="shared" ref="G16" si="18">F16*7</f>
+        <v>147</v>
+      </c>
+      <c r="H16" s="25">
         <v>12</v>
       </c>
-      <c r="C17" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="17">
-        <v>45169</v>
-      </c>
-      <c r="F17" s="23"/>
+      <c r="I16" s="25">
+        <v>6</v>
+      </c>
+      <c r="J16" s="25">
+        <f t="shared" ref="J16" si="19">H16*12</f>
+        <v>144</v>
+      </c>
+      <c r="K16" s="25">
+        <f t="shared" ref="K16:K25" si="20">I16*24</f>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="24">
+        <v>46265</v>
+      </c>
+      <c r="F17" s="25"/>
       <c r="G17" s="25"/>
       <c r="H17" s="25"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="27"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="E18" s="16">
-        <v>45170</v>
-      </c>
-      <c r="F18" s="22">
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="24">
+        <v>46266</v>
+      </c>
+      <c r="F18" s="25">
         <f>NETWORKDAYS(E18,E19,A2:A31)</f>
-        <v>21</v>
-      </c>
-      <c r="G18" s="24">
-        <f t="shared" ref="G18" si="14">F18*7</f>
-        <v>147</v>
-      </c>
-      <c r="H18" s="24">
-        <v>12</v>
-      </c>
-      <c r="I18" s="22">
-        <v>6</v>
-      </c>
-      <c r="J18" s="26">
-        <f t="shared" ref="J18" si="15">H18*12</f>
-        <v>144</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E19" s="17">
-        <v>45199</v>
-      </c>
-      <c r="F19" s="23"/>
+        <v>22</v>
+      </c>
+      <c r="G18" s="25">
+        <f t="shared" ref="G18" si="21">F18*7</f>
+        <v>154</v>
+      </c>
+      <c r="H18" s="25">
+        <v>13</v>
+      </c>
+      <c r="I18" s="25">
+        <v>6.5</v>
+      </c>
+      <c r="J18" s="25">
+        <f t="shared" ref="J18" si="22">H18*12</f>
+        <v>156</v>
+      </c>
+      <c r="K18" s="25">
+        <f t="shared" ref="K18:K25" si="23">I18*24</f>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46387</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="24">
+        <v>46295</v>
+      </c>
+      <c r="F19" s="25"/>
       <c r="G19" s="25"/>
       <c r="H19" s="25"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="27"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E20" s="16">
-        <v>45200</v>
-      </c>
-      <c r="F20" s="22">
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E20" s="24">
+        <v>46296</v>
+      </c>
+      <c r="F20" s="25">
         <f>NETWORKDAYS(E20,E21,A2:A31)</f>
-        <v>22</v>
-      </c>
-      <c r="G20" s="24">
-        <f t="shared" ref="G20" si="16">F20*7</f>
-        <v>154</v>
-      </c>
-      <c r="H20" s="24">
-        <v>13</v>
-      </c>
-      <c r="I20" s="22">
-        <v>6.5</v>
-      </c>
-      <c r="J20" s="26">
-        <f t="shared" ref="J20" si="17">H20*12</f>
-        <v>156</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E21" s="17">
-        <v>45230</v>
-      </c>
-      <c r="F21" s="23"/>
+        <v>20</v>
+      </c>
+      <c r="G20" s="25">
+        <f t="shared" ref="G20" si="24">F20*7</f>
+        <v>140</v>
+      </c>
+      <c r="H20" s="25">
+        <v>12</v>
+      </c>
+      <c r="I20" s="25">
+        <v>6</v>
+      </c>
+      <c r="J20" s="25">
+        <f t="shared" ref="J20" si="25">H20*12</f>
+        <v>144</v>
+      </c>
+      <c r="K20" s="25">
+        <f t="shared" ref="K20:K25" si="26">I20*24</f>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E21" s="24">
+        <v>46326</v>
+      </c>
+      <c r="F21" s="25"/>
       <c r="G21" s="25"/>
       <c r="H21" s="25"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="27"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E22" s="16">
-        <v>45231</v>
-      </c>
-      <c r="F22" s="22">
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E22" s="24">
+        <v>46327</v>
+      </c>
+      <c r="F22" s="25">
         <f>NETWORKDAYS(E22,E23,A2:A31)</f>
-        <v>22</v>
-      </c>
-      <c r="G22" s="24">
-        <f t="shared" ref="G22" si="18">F22*7</f>
-        <v>154</v>
-      </c>
-      <c r="H22" s="24">
-        <v>13</v>
-      </c>
-      <c r="I22" s="22">
-        <v>6.5</v>
-      </c>
-      <c r="J22" s="26">
-        <f t="shared" ref="J22" si="19">H22*12</f>
-        <v>156</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E23" s="17">
-        <v>45260</v>
-      </c>
-      <c r="F23" s="23"/>
+        <v>21</v>
+      </c>
+      <c r="G22" s="25">
+        <f t="shared" ref="G22" si="27">F22*7</f>
+        <v>147</v>
+      </c>
+      <c r="H22" s="25">
+        <v>12</v>
+      </c>
+      <c r="I22" s="25">
+        <v>6</v>
+      </c>
+      <c r="J22" s="25">
+        <f t="shared" ref="J22" si="28">H22*12</f>
+        <v>144</v>
+      </c>
+      <c r="K22" s="25">
+        <f t="shared" ref="K22:K25" si="29">I22*24</f>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E23" s="24">
+        <v>46356</v>
+      </c>
+      <c r="F23" s="25"/>
       <c r="G23" s="25"/>
       <c r="H23" s="25"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="27"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E24" s="16">
-        <v>45261</v>
-      </c>
-      <c r="F24" s="22">
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E24" s="24">
+        <v>46357</v>
+      </c>
+      <c r="F24" s="25">
         <f>NETWORKDAYS(E24,E25,A2:A31)</f>
-        <v>21</v>
-      </c>
-      <c r="G24" s="24">
-        <f t="shared" ref="G24" si="20">F24*7</f>
-        <v>147</v>
-      </c>
-      <c r="H24" s="24">
-        <v>12</v>
-      </c>
-      <c r="I24" s="22">
-        <v>6</v>
-      </c>
-      <c r="J24" s="26">
-        <f t="shared" ref="J24" si="21">H24*12</f>
-        <v>144</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E25" s="17">
-        <v>45291</v>
-      </c>
-      <c r="F25" s="23"/>
+        <v>22</v>
+      </c>
+      <c r="G24" s="25">
+        <f t="shared" ref="G24" si="30">F24*7</f>
+        <v>154</v>
+      </c>
+      <c r="H24" s="25">
+        <v>13</v>
+      </c>
+      <c r="I24" s="25">
+        <v>6.5</v>
+      </c>
+      <c r="J24" s="25">
+        <f t="shared" ref="J24" si="31">H24*12</f>
+        <v>156</v>
+      </c>
+      <c r="K24" s="25">
+        <f t="shared" ref="K24:K25" si="32">I24*24</f>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E25" s="24">
+        <v>46387</v>
+      </c>
+      <c r="F25" s="25"/>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="27"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E26" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="22">
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E26" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" s="25">
         <f>SUM(F2:F25)</f>
-        <v>251</v>
-      </c>
-      <c r="G26" s="22">
+        <v>247</v>
+      </c>
+      <c r="G26" s="25">
         <f>SUM(G2:G25)</f>
-        <v>1757</v>
-      </c>
-      <c r="H26" s="24">
+        <v>1729</v>
+      </c>
+      <c r="H26" s="25">
         <f>SUM(H2:H25)</f>
-        <v>146</v>
-      </c>
-      <c r="I26" s="24">
+        <v>145</v>
+      </c>
+      <c r="I26" s="25">
         <f>SUM(I2:I25)</f>
-        <v>73</v>
-      </c>
-      <c r="J26" s="26">
+        <v>72.5</v>
+      </c>
+      <c r="J26" s="25">
         <f>H26*12</f>
-        <v>1752</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E27" s="21"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
+        <v>1740</v>
+      </c>
+      <c r="K26" s="25">
+        <f>I26*24</f>
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E27" s="26"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
       <c r="H27" s="25"/>
       <c r="I27" s="25"/>
-      <c r="J27" s="27"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="66">
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="I4:I5"/>
+  <mergeCells count="79">
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="K10:K11"/>
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="F2:F3"/>
@@ -2872,8 +2817,60 @@
     <mergeCell ref="F20:F21"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="I26:I27"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
